--- a/data/trans_orig/P29A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>393631</t>
+          <t>391106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>443647</t>
+          <t>440197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140276</t>
+          <t>140593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183809</t>
+          <t>184548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>544229</t>
+          <t>544019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>613705</t>
+          <t>614982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242563</t>
+          <t>246013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292579</t>
+          <t>295104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>502564</t>
+          <t>501825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>546097</t>
+          <t>545780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758878</t>
+          <t>757601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>828354</t>
+          <t>828564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>524132</t>
+          <t>523648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>586073</t>
+          <t>585586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>225266</t>
+          <t>223454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>278791</t>
+          <t>277692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>759294</t>
+          <t>762797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>848103</t>
+          <t>854482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362997</t>
+          <t>363484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>424938</t>
+          <t>425422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>682000</t>
+          <t>683099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>735525</t>
+          <t>737337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1061757</t>
+          <t>1055378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150566</t>
+          <t>1147063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>281049</t>
+          <t>278066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>332628</t>
+          <t>330419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103258</t>
+          <t>103873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141259</t>
+          <t>142157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390290</t>
+          <t>391388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>455444</t>
+          <t>459073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>333938</t>
+          <t>336147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>385517</t>
+          <t>388500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538363</t>
+          <t>537465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576364</t>
+          <t>575749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>890745</t>
+          <t>887116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>955899</t>
+          <t>954801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>469751</t>
+          <t>467812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>528141</t>
+          <t>529586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>259897</t>
+          <t>263197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>318518</t>
+          <t>317338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>747335</t>
+          <t>746416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>830574</t>
+          <t>828180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>402616</t>
+          <t>401171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>461006</t>
+          <t>462945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>714975</t>
+          <t>716155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>773596</t>
+          <t>770296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1133676</t>
+          <t>1136070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1216915</t>
+          <t>1217834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1721081</t>
+          <t>1711533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1830050</t>
+          <t>1832417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>774438</t>
+          <t>776264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>871859</t>
+          <t>875351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2521204</t>
+          <t>2521776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2681089</t>
+          <t>2683702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1402553</t>
+          <t>1400186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1511522</t>
+          <t>1521070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2488420</t>
+          <t>2484928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2585841</t>
+          <t>2584015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3911793</t>
+          <t>3909180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4071678</t>
+          <t>4071106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012 (tasa de respuesta: 96,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>357570</t>
+          <t>356505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>408530</t>
+          <t>407727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128141</t>
+          <t>127990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171625</t>
+          <t>172776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>495316</t>
+          <t>495051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>569616</t>
+          <t>566165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260661</t>
+          <t>261464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311621</t>
+          <t>312686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>519537</t>
+          <t>518386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>563021</t>
+          <t>563172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>790737</t>
+          <t>794188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>865037</t>
+          <t>865302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>506294</t>
+          <t>505494</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>572616</t>
+          <t>570501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220319</t>
+          <t>219455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>277019</t>
+          <t>276793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>743148</t>
+          <t>740203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>832629</t>
+          <t>832365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402233</t>
+          <t>404348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>468555</t>
+          <t>469355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730106</t>
+          <t>730332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>786806</t>
+          <t>787670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149346</t>
+          <t>1149610</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1238827</t>
+          <t>1241772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>376149</t>
+          <t>374544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>429222</t>
+          <t>431088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152242</t>
+          <t>154574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203127</t>
+          <t>203408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>538577</t>
+          <t>541315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>622236</t>
+          <t>623400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288987</t>
+          <t>287121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342060</t>
+          <t>343665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553361</t>
+          <t>553080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>604246</t>
+          <t>601914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>852461</t>
+          <t>851297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936120</t>
+          <t>933382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>483570</t>
+          <t>483927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>544252</t>
+          <t>547822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290984</t>
+          <t>290229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>352991</t>
+          <t>349179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>791241</t>
+          <t>792309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>880568</t>
+          <t>883426</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368074</t>
+          <t>364504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>428756</t>
+          <t>428399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678375</t>
+          <t>682187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>740382</t>
+          <t>741137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1063124</t>
+          <t>1060266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1152451</t>
+          <t>1151383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1779918</t>
+          <t>1778373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1902363</t>
+          <t>1900727</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>846381</t>
+          <t>846842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>953364</t>
+          <t>949519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2656385</t>
+          <t>2647611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2820098</t>
+          <t>2819507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1372213</t>
+          <t>1373849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1494658</t>
+          <t>1496203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2532777</t>
+          <t>2536622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2639760</t>
+          <t>2639299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3940618</t>
+          <t>3941209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4104331</t>
+          <t>4113105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016 (tasa de respuesta: 97,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>365746</t>
+          <t>365243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>413927</t>
+          <t>413843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155357</t>
+          <t>151389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>197476</t>
+          <t>196636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531199</t>
+          <t>529214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>600672</t>
+          <t>598632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229094</t>
+          <t>229178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277275</t>
+          <t>277778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>470644</t>
+          <t>471484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512763</t>
+          <t>516731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>710469</t>
+          <t>712509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>779942</t>
+          <t>781927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>503255</t>
+          <t>502899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>570152</t>
+          <t>564985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>264875</t>
+          <t>264082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324861</t>
+          <t>324999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>781522</t>
+          <t>784488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>874128</t>
+          <t>880048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421099</t>
+          <t>426266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487996</t>
+          <t>488352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>697939</t>
+          <t>697801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>757925</t>
+          <t>758718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1139923</t>
+          <t>1134003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1232529</t>
+          <t>1229563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>376273</t>
+          <t>378472</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>430358</t>
+          <t>431075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191537</t>
+          <t>191187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>242125</t>
+          <t>243681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>580720</t>
+          <t>584205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>661406</t>
+          <t>664041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312019</t>
+          <t>311302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>366104</t>
+          <t>363905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529331</t>
+          <t>527775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>579919</t>
+          <t>580269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>852426</t>
+          <t>849791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933112</t>
+          <t>929627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>516787</t>
+          <t>517903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>576746</t>
+          <t>573885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>353927</t>
+          <t>357643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>420280</t>
+          <t>421418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>888630</t>
+          <t>886777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>980301</t>
+          <t>975058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334151</t>
+          <t>337012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>394110</t>
+          <t>392994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>605409</t>
+          <t>604271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>671762</t>
+          <t>668046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>956285</t>
+          <t>961528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1047956</t>
+          <t>1049809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1821769</t>
+          <t>1819409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1933711</t>
+          <t>1934282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1019800</t>
+          <t>1016079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1131476</t>
+          <t>1129875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2868467</t>
+          <t>2873027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3039082</t>
+          <t>3037583</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1353835</t>
+          <t>1353264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1465777</t>
+          <t>1468137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2356588</t>
+          <t>2358189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2468264</t>
+          <t>2471985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3736528</t>
+          <t>3738027</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3907143</t>
+          <t>3902583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>303361</t>
+          <t>305231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>360260</t>
+          <t>361430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141184</t>
+          <t>140191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178881</t>
+          <t>178184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>458327</t>
+          <t>459805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>529039</t>
+          <t>528898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272974</t>
+          <t>271804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329873</t>
+          <t>328003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>495815</t>
+          <t>496512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>533512</t>
+          <t>534505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>778891</t>
+          <t>779032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>849603</t>
+          <t>848125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>263859</t>
+          <t>225056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>614494</t>
+          <t>616152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180423</t>
+          <t>178114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>226954</t>
+          <t>225282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461103</t>
+          <t>454988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>778568</t>
+          <t>786509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577256</t>
+          <t>575598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>927891</t>
+          <t>966694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>729538</t>
+          <t>731210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>776069</t>
+          <t>778378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1369674</t>
+          <t>1361733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1687139</t>
+          <t>1693254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>297067</t>
+          <t>293950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359436</t>
+          <t>356269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208501</t>
+          <t>208454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>672492</t>
+          <t>627227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>551567</t>
+          <t>551488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1092162</t>
+          <t>1024127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>342883</t>
+          <t>346050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>405252</t>
+          <t>408369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258594</t>
+          <t>303859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>722585</t>
+          <t>722632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541243</t>
+          <t>609278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1081838</t>
+          <t>1081917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>407436</t>
+          <t>405339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>477578</t>
+          <t>474518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225737</t>
+          <t>231709</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>319803</t>
+          <t>325525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>642202</t>
+          <t>646212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>786020</t>
+          <t>785210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>448167</t>
+          <t>451227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>518309</t>
+          <t>520406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>770269</t>
+          <t>764547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>864335</t>
+          <t>858363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1229797</t>
+          <t>1230607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1373615</t>
+          <t>1369605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1248887</t>
+          <t>1200308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1719386</t>
+          <t>1723251</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>851493</t>
+          <t>850746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1468125</t>
+          <t>1518369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2375497</t>
+          <t>2351846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3032422</t>
+          <t>3000156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1733662</t>
+          <t>1729797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2204161</t>
+          <t>2252740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2184221</t>
+          <t>2133977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2800853</t>
+          <t>2801600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4072973</t>
+          <t>4105239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4729898</t>
+          <t>4753549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>391106</t>
+          <t>388173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>440197</t>
+          <t>443390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140593</t>
+          <t>141561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184548</t>
+          <t>183754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>544019</t>
+          <t>542505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>614982</t>
+          <t>615453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246013</t>
+          <t>242820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295104</t>
+          <t>298037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>501825</t>
+          <t>502619</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>545780</t>
+          <t>544812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757601</t>
+          <t>757130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>828564</t>
+          <t>830078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>523648</t>
+          <t>523841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>585586</t>
+          <t>586630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223454</t>
+          <t>222394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>277692</t>
+          <t>278502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>762797</t>
+          <t>762898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>854482</t>
+          <t>848919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363484</t>
+          <t>362440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425422</t>
+          <t>425229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>683099</t>
+          <t>682289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>737337</t>
+          <t>738397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1055378</t>
+          <t>1060941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1147063</t>
+          <t>1146962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>278066</t>
+          <t>276805</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>330419</t>
+          <t>329445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103873</t>
+          <t>103774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142157</t>
+          <t>143665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391388</t>
+          <t>393546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459073</t>
+          <t>460473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336147</t>
+          <t>337121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>388500</t>
+          <t>389761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537465</t>
+          <t>535957</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575749</t>
+          <t>575848</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>887116</t>
+          <t>885716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>954801</t>
+          <t>952643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>467812</t>
+          <t>473407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>529586</t>
+          <t>532877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263197</t>
+          <t>259613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>317338</t>
+          <t>318185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>746416</t>
+          <t>741604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>828180</t>
+          <t>829844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>401171</t>
+          <t>397880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>462945</t>
+          <t>457350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>716155</t>
+          <t>715308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>770296</t>
+          <t>773880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1136070</t>
+          <t>1134406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1217834</t>
+          <t>1222646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1711533</t>
+          <t>1720474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1832417</t>
+          <t>1832180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>776264</t>
+          <t>771836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>875351</t>
+          <t>872284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2521776</t>
+          <t>2512024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2683702</t>
+          <t>2675544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1400186</t>
+          <t>1400423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1521070</t>
+          <t>1512129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2484928</t>
+          <t>2487995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2584015</t>
+          <t>2588443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3909180</t>
+          <t>3917338</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4071106</t>
+          <t>4080858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>356505</t>
+          <t>356503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>407727</t>
+          <t>408306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127990</t>
+          <t>127969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172776</t>
+          <t>171190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>495051</t>
+          <t>490705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>566165</t>
+          <t>566379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261464</t>
+          <t>260885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312686</t>
+          <t>312688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>518386</t>
+          <t>519972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>563172</t>
+          <t>563193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794188</t>
+          <t>793974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>865302</t>
+          <t>869648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505494</t>
+          <t>507777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>570501</t>
+          <t>572534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219455</t>
+          <t>217129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>276793</t>
+          <t>277211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>740203</t>
+          <t>738763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>832365</t>
+          <t>830133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404348</t>
+          <t>402315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469355</t>
+          <t>467072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730332</t>
+          <t>729914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>787670</t>
+          <t>789996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149610</t>
+          <t>1151842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1241772</t>
+          <t>1243212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>374544</t>
+          <t>373659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>431088</t>
+          <t>430243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154574</t>
+          <t>156013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203408</t>
+          <t>206182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>541315</t>
+          <t>542995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>623400</t>
+          <t>619627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287121</t>
+          <t>287966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343665</t>
+          <t>344550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553080</t>
+          <t>550306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>601914</t>
+          <t>600475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>851297</t>
+          <t>855070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933382</t>
+          <t>931702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>483927</t>
+          <t>481333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>547822</t>
+          <t>542961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290229</t>
+          <t>291145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349179</t>
+          <t>350064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>792309</t>
+          <t>789262</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>883426</t>
+          <t>878328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,19%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364504</t>
+          <t>369365</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>428399</t>
+          <t>430993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682187</t>
+          <t>681302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741137</t>
+          <t>740221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1060266</t>
+          <t>1065364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1151383</t>
+          <t>1154430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1778373</t>
+          <t>1775043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1900727</t>
+          <t>1894175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>846842</t>
+          <t>846100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>949519</t>
+          <t>953775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2647611</t>
+          <t>2645986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2819507</t>
+          <t>2819861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1373849</t>
+          <t>1380401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1496203</t>
+          <t>1499533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2536622</t>
+          <t>2532366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2639299</t>
+          <t>2640041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3941209</t>
+          <t>3940855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4113105</t>
+          <t>4114730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>365243</t>
+          <t>365683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>413843</t>
+          <t>412926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151389</t>
+          <t>154662</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>196636</t>
+          <t>198875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>529214</t>
+          <t>527109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>598632</t>
+          <t>598819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229178</t>
+          <t>230095</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277778</t>
+          <t>277338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>471484</t>
+          <t>469245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>516731</t>
+          <t>513458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712509</t>
+          <t>712322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>781927</t>
+          <t>784032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,8%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>502899</t>
+          <t>506760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>564985</t>
+          <t>570040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>264082</t>
+          <t>267119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324999</t>
+          <t>324507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>784488</t>
+          <t>786588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>880048</t>
+          <t>873585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426266</t>
+          <t>421211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488352</t>
+          <t>484491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>697801</t>
+          <t>698293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>758718</t>
+          <t>755681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134003</t>
+          <t>1140466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1229563</t>
+          <t>1227463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>378472</t>
+          <t>377857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>431075</t>
+          <t>437388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191187</t>
+          <t>192336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>243681</t>
+          <t>242467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>584205</t>
+          <t>583831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>664041</t>
+          <t>660892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311302</t>
+          <t>304989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>363905</t>
+          <t>364520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527775</t>
+          <t>528989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>580269</t>
+          <t>579120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>849791</t>
+          <t>852940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>929627</t>
+          <t>930001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>517903</t>
+          <t>516538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>573885</t>
+          <t>576387</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>357643</t>
+          <t>354654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>421418</t>
+          <t>420314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>886777</t>
+          <t>891023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>975058</t>
+          <t>980218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337012</t>
+          <t>334510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>392994</t>
+          <t>394359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604271</t>
+          <t>605375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>668046</t>
+          <t>671035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>961528</t>
+          <t>956368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1049809</t>
+          <t>1045563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1819409</t>
+          <t>1819001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1934282</t>
+          <t>1933753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1016079</t>
+          <t>1017218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1129875</t>
+          <t>1127265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2873027</t>
+          <t>2865621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3037583</t>
+          <t>3032254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1353264</t>
+          <t>1353793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1468137</t>
+          <t>1468545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2358189</t>
+          <t>2360799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2471985</t>
+          <t>2470846</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3738027</t>
+          <t>3743356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3902583</t>
+          <t>3909989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>333157</t>
+          <t>353514</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>305231</t>
+          <t>322362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>361430</t>
+          <t>381310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>159637</t>
+          <t>172651</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140191</t>
+          <t>155344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178184</t>
+          <t>194168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>492794</t>
+          <t>526165</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>459805</t>
+          <t>487700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>528898</t>
+          <t>561588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>300077</t>
+          <t>334936</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271804</t>
+          <t>307140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>328003</t>
+          <t>366088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>515059</t>
+          <t>559352</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>496512</t>
+          <t>537835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>534505</t>
+          <t>576659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>815136</t>
+          <t>894288</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>779032</t>
+          <t>858865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>848125</t>
+          <t>932753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633234</t>
+          <t>688450</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633234</t>
+          <t>688450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633234</t>
+          <t>688450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674696</t>
+          <t>732003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674696</t>
+          <t>732003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674696</t>
+          <t>732003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1307930</t>
+          <t>1420453</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1307930</t>
+          <t>1420453</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1307930</t>
+          <t>1420453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>476919</t>
+          <t>501905</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>225056</t>
+          <t>467336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>616152</t>
+          <t>539831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>201444</t>
+          <t>223193</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178114</t>
+          <t>200456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225282</t>
+          <t>250048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>678363</t>
+          <t>725098</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>454988</t>
+          <t>680883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>786509</t>
+          <t>769692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>714831</t>
+          <t>545828</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575598</t>
+          <t>507902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>966694</t>
+          <t>580397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>755048</t>
+          <t>845326</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>731210</t>
+          <t>818471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>778378</t>
+          <t>868063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1469879</t>
+          <t>1391154</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1361733</t>
+          <t>1346560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1693254</t>
+          <t>1435369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191750</t>
+          <t>1047733</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191750</t>
+          <t>1047733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191750</t>
+          <t>1047733</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956492</t>
+          <t>1068519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956492</t>
+          <t>1068519</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956492</t>
+          <t>1068519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148242</t>
+          <t>2116252</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148242</t>
+          <t>2116252</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148242</t>
+          <t>2116252</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>326527</t>
+          <t>361328</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>293950</t>
+          <t>329331</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>356269</t>
+          <t>393152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208454</t>
+          <t>180355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>627227</t>
+          <t>224923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>702624</t>
+          <t>562462</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>551488</t>
+          <t>523704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1024127</t>
+          <t>602100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>375792</t>
+          <t>438309</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>346050</t>
+          <t>406485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>408369</t>
+          <t>470306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>554989</t>
+          <t>608504</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303859</t>
+          <t>584715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>722632</t>
+          <t>629283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>930781</t>
+          <t>1046813</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609278</t>
+          <t>1007175</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1081917</t>
+          <t>1085571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702319</t>
+          <t>799637</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702319</t>
+          <t>799637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702319</t>
+          <t>799637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931086</t>
+          <t>809638</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931086</t>
+          <t>809638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931086</t>
+          <t>809638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633405</t>
+          <t>1609275</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633405</t>
+          <t>1609275</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633405</t>
+          <t>1609275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>405339</t>
+          <t>429425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>474518</t>
+          <t>497530</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291013</t>
+          <t>310671</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231709</t>
+          <t>284627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>325525</t>
+          <t>338332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>734712</t>
+          <t>776336</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646212</t>
+          <t>730562</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>785210</t>
+          <t>820642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>482045</t>
+          <t>523301</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>451227</t>
+          <t>491435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>520406</t>
+          <t>559540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>799059</t>
+          <t>804923</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>764547</t>
+          <t>777262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>858363</t>
+          <t>830967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1281105</t>
+          <t>1328223</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1230607</t>
+          <t>1283917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1369605</t>
+          <t>1373997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>65,29%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925745</t>
+          <t>988965</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925745</t>
+          <t>988965</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925745</t>
+          <t>988965</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090072</t>
+          <t>1115594</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090072</t>
+          <t>1115594</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090072</t>
+          <t>1115594</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2015817</t>
+          <t>2104559</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2015817</t>
+          <t>2104559</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2015817</t>
+          <t>2104559</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1580302</t>
+          <t>1682411</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1200308</t>
+          <t>1614562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1723251</t>
+          <t>1751951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1028192</t>
+          <t>907649</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>850746</t>
+          <t>859504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1518369</t>
+          <t>958057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2608494</t>
+          <t>2590061</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2351846</t>
+          <t>2494475</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3000156</t>
+          <t>2670491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1872746</t>
+          <t>1842374</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1729797</t>
+          <t>1772834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2252740</t>
+          <t>1910223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2624154</t>
+          <t>2818105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2133977</t>
+          <t>2767697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2801600</t>
+          <t>2866250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4496901</t>
+          <t>4660478</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4105239</t>
+          <t>4580048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4753549</t>
+          <t>4756064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
